--- a/result/Table202511.xlsx
+++ b/result/Table202511.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -525,19 +525,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I2" t="n">
         <v>9.16</v>
       </c>
       <c r="J2" t="n">
-        <v>5.49</v>
+        <v>5.4</v>
       </c>
       <c r="K2" t="n">
-        <v>-40.07</v>
+        <v>-41.05</v>
       </c>
       <c r="L2" t="n">
-        <v>-40065.5</v>
+        <v>-41048.03</v>
       </c>
     </row>
     <row r="3">
@@ -566,7 +566,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,19 +575,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I3" t="n">
         <v>12.59</v>
       </c>
       <c r="J3" t="n">
-        <v>8.699999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>-30.9</v>
+        <v>-30.18</v>
       </c>
       <c r="L3" t="n">
-        <v>-30897.54</v>
+        <v>-30182.68</v>
       </c>
     </row>
     <row r="4">
@@ -716,7 +716,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I6" t="n">
         <v>5.76</v>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I24" t="n">
         <v>41.42</v>
       </c>
       <c r="J24" t="n">
-        <v>27</v>
+        <v>26.27</v>
       </c>
       <c r="K24" t="n">
-        <v>-34.81</v>
+        <v>-36.58</v>
       </c>
       <c r="L24" t="n">
-        <v>-34814.1</v>
+        <v>-36576.53</v>
       </c>
     </row>
     <row r="25">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I35" t="n">
         <v>10.64</v>
       </c>
       <c r="J35" t="n">
-        <v>7.65</v>
+        <v>7.55</v>
       </c>
       <c r="K35" t="n">
-        <v>-28.1</v>
+        <v>-29.04</v>
       </c>
       <c r="L35" t="n">
-        <v>-28101.5</v>
+        <v>-29041.35</v>
       </c>
     </row>
     <row r="36">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3967,19 +3967,19 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I73" t="n">
         <v>21.93</v>
       </c>
       <c r="J73" t="n">
-        <v>11.43</v>
+        <v>11.42</v>
       </c>
       <c r="K73" t="n">
-        <v>-47.88</v>
+        <v>-47.93</v>
       </c>
       <c r="L73" t="n">
-        <v>-47879.62</v>
+        <v>-47925.22</v>
       </c>
     </row>
     <row r="74">

--- a/result/Table202511.xlsx
+++ b/result/Table202511.xlsx
@@ -1012,24 +1012,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
         <v>13.71</v>
       </c>
       <c r="J12" t="n">
-        <v>12.35</v>
+        <v>11.11</v>
       </c>
       <c r="K12" t="n">
-        <v>-9.92</v>
+        <v>-18.96</v>
       </c>
       <c r="L12" t="n">
-        <v>-9919.77</v>
+        <v>-18964.26</v>
       </c>
     </row>
     <row r="13">
@@ -1108,24 +1108,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I14" t="n">
         <v>11.15</v>
       </c>
       <c r="J14" t="n">
-        <v>10.23</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-8.25</v>
+        <v>-10.58</v>
       </c>
       <c r="L14" t="n">
-        <v>-8251.120000000001</v>
+        <v>-10582.96</v>
       </c>
     </row>
     <row r="15">
@@ -1204,24 +1204,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
         <v>9.74</v>
       </c>
       <c r="J16" t="n">
-        <v>9.25</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.03</v>
+        <v>-11.6</v>
       </c>
       <c r="L16" t="n">
-        <v>-5030.8</v>
+        <v>-11601.64</v>
       </c>
     </row>
     <row r="17">
@@ -1250,24 +1250,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I17" t="n">
         <v>7.81</v>
       </c>
       <c r="J17" t="n">
-        <v>7.46</v>
+        <v>6.95</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.48</v>
+        <v>-11.01</v>
       </c>
       <c r="L17" t="n">
-        <v>-4481.43</v>
+        <v>-11011.52</v>
       </c>
     </row>
     <row r="18">
@@ -2084,24 +2084,24 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I34" t="n">
         <v>21.07</v>
       </c>
       <c r="J34" t="n">
-        <v>29.07</v>
+        <v>28.1</v>
       </c>
       <c r="K34" t="n">
-        <v>37.97</v>
+        <v>33.36</v>
       </c>
       <c r="L34" t="n">
-        <v>37968.68</v>
+        <v>33364.97</v>
       </c>
     </row>
     <row r="35">
@@ -2768,24 +2768,24 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I48" t="n">
         <v>30.72</v>
       </c>
       <c r="J48" t="n">
-        <v>29.84</v>
+        <v>28.92</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.86</v>
+        <v>-5.86</v>
       </c>
       <c r="L48" t="n">
-        <v>-2864.58</v>
+        <v>-5859.37</v>
       </c>
     </row>
     <row r="49">
@@ -2960,24 +2960,24 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I52" t="n">
         <v>12.71</v>
       </c>
       <c r="J52" t="n">
-        <v>12.66</v>
+        <v>12.07</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.39</v>
+        <v>-5.04</v>
       </c>
       <c r="L52" t="n">
-        <v>-393.39</v>
+        <v>-5035.41</v>
       </c>
     </row>
     <row r="53">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I54" t="n">
         <v>49.89</v>
       </c>
       <c r="J54" t="n">
-        <v>56.18</v>
+        <v>52.95</v>
       </c>
       <c r="K54" t="n">
-        <v>12.61</v>
+        <v>6.13</v>
       </c>
       <c r="L54" t="n">
-        <v>12607.74</v>
+        <v>6133.49</v>
       </c>
     </row>
     <row r="55">
@@ -3336,24 +3336,24 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I60" t="n">
         <v>13.33</v>
       </c>
       <c r="J60" t="n">
-        <v>12.46</v>
+        <v>11.38</v>
       </c>
       <c r="K60" t="n">
-        <v>-6.53</v>
+        <v>-14.63</v>
       </c>
       <c r="L60" t="n">
-        <v>-6526.63</v>
+        <v>-14628.66</v>
       </c>
     </row>
     <row r="61">
@@ -3482,24 +3482,24 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I63" t="n">
         <v>5.35</v>
       </c>
       <c r="J63" t="n">
-        <v>5.08</v>
+        <v>4.73</v>
       </c>
       <c r="K63" t="n">
-        <v>-5.05</v>
+        <v>-11.59</v>
       </c>
       <c r="L63" t="n">
-        <v>-5046.73</v>
+        <v>-11588.79</v>
       </c>
     </row>
     <row r="64">
@@ -3678,24 +3678,24 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I67" t="n">
         <v>7.46</v>
       </c>
       <c r="J67" t="n">
-        <v>7.39</v>
+        <v>7.23</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-3.08</v>
       </c>
       <c r="L67" t="n">
-        <v>-938.34</v>
+        <v>-3083.11</v>
       </c>
     </row>
     <row r="68">
@@ -3724,24 +3724,24 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I68" t="n">
         <v>4.08</v>
       </c>
       <c r="J68" t="n">
-        <v>3.74</v>
+        <v>8.49</v>
       </c>
       <c r="K68" t="n">
-        <v>-8.33</v>
+        <v>108.09</v>
       </c>
       <c r="L68" t="n">
-        <v>-8333.33</v>
+        <v>108088.24</v>
       </c>
     </row>
     <row r="69">
@@ -3770,24 +3770,24 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I69" t="n">
         <v>22.53</v>
       </c>
       <c r="J69" t="n">
-        <v>21</v>
+        <v>19.85</v>
       </c>
       <c r="K69" t="n">
-        <v>-6.79</v>
+        <v>-11.9</v>
       </c>
       <c r="L69" t="n">
-        <v>-6790.95</v>
+        <v>-11895.25</v>
       </c>
     </row>
     <row r="70">
@@ -3816,24 +3816,24 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I70" t="n">
         <v>14.01</v>
       </c>
       <c r="J70" t="n">
-        <v>15.73</v>
+        <v>14.96</v>
       </c>
       <c r="K70" t="n">
-        <v>12.28</v>
+        <v>6.78</v>
       </c>
       <c r="L70" t="n">
-        <v>12276.95</v>
+        <v>6780.87</v>
       </c>
     </row>
     <row r="71">
@@ -3862,24 +3862,24 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I71" t="n">
         <v>5.16</v>
       </c>
       <c r="J71" t="n">
-        <v>4.74</v>
+        <v>4.61</v>
       </c>
       <c r="K71" t="n">
-        <v>-8.140000000000001</v>
+        <v>-10.66</v>
       </c>
       <c r="L71" t="n">
-        <v>-8139.53</v>
+        <v>-10658.91</v>
       </c>
     </row>
     <row r="72">
@@ -4008,24 +4008,24 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="I74" t="n">
         <v>3.42</v>
       </c>
       <c r="J74" t="n">
-        <v>3.12</v>
+        <v>4.05</v>
       </c>
       <c r="K74" t="n">
-        <v>-8.77</v>
+        <v>18.42</v>
       </c>
       <c r="L74" t="n">
-        <v>-8771.93</v>
+        <v>18421.05</v>
       </c>
     </row>
     <row r="75">
@@ -4054,24 +4054,24 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I75" t="n">
         <v>28.5</v>
       </c>
       <c r="J75" t="n">
-        <v>27</v>
+        <v>24.93</v>
       </c>
       <c r="K75" t="n">
-        <v>-5.26</v>
+        <v>-12.53</v>
       </c>
       <c r="L75" t="n">
-        <v>-5263.16</v>
+        <v>-12526.32</v>
       </c>
     </row>
     <row r="76">
@@ -4150,24 +4150,24 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I77" t="n">
         <v>11.02</v>
       </c>
       <c r="J77" t="n">
-        <v>12.01</v>
+        <v>10.5</v>
       </c>
       <c r="K77" t="n">
-        <v>8.98</v>
+        <v>-4.72</v>
       </c>
       <c r="L77" t="n">
-        <v>8983.67</v>
+        <v>-4718.69</v>
       </c>
     </row>
     <row r="78">

--- a/result/Table202511.xlsx
+++ b/result/Table202511.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -525,19 +525,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I2" t="n">
         <v>9.16</v>
       </c>
       <c r="J2" t="n">
-        <v>5.4</v>
+        <v>5.33</v>
       </c>
       <c r="K2" t="n">
-        <v>-41.05</v>
+        <v>-41.81</v>
       </c>
       <c r="L2" t="n">
-        <v>-41048.03</v>
+        <v>-41812.23</v>
       </c>
     </row>
     <row r="3">
@@ -566,7 +566,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,19 +575,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I3" t="n">
         <v>12.59</v>
       </c>
       <c r="J3" t="n">
-        <v>8.789999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="K3" t="n">
-        <v>-30.18</v>
+        <v>-30.98</v>
       </c>
       <c r="L3" t="n">
-        <v>-30182.68</v>
+        <v>-30976.97</v>
       </c>
     </row>
     <row r="4">
@@ -716,7 +716,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I6" t="n">
         <v>5.76</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="K6" t="n">
-        <v>-37.5</v>
+        <v>-39.41</v>
       </c>
       <c r="L6" t="n">
-        <v>-37500</v>
+        <v>-39409.72</v>
       </c>
     </row>
     <row r="7">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I24" t="n">
         <v>41.42</v>
       </c>
       <c r="J24" t="n">
-        <v>26.27</v>
+        <v>26.28</v>
       </c>
       <c r="K24" t="n">
-        <v>-36.58</v>
+        <v>-36.55</v>
       </c>
       <c r="L24" t="n">
-        <v>-36576.53</v>
+        <v>-36552.39</v>
       </c>
     </row>
     <row r="25">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="I35" t="n">
         <v>10.64</v>
       </c>
       <c r="J35" t="n">
-        <v>7.55</v>
+        <v>7.44</v>
       </c>
       <c r="K35" t="n">
-        <v>-29.04</v>
+        <v>-30.08</v>
       </c>
       <c r="L35" t="n">
-        <v>-29041.35</v>
+        <v>-30075.19</v>
       </c>
     </row>
     <row r="36">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3967,19 +3967,19 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I73" t="n">
         <v>21.93</v>
       </c>
       <c r="J73" t="n">
-        <v>11.42</v>
+        <v>11.52</v>
       </c>
       <c r="K73" t="n">
-        <v>-47.93</v>
+        <v>-47.47</v>
       </c>
       <c r="L73" t="n">
-        <v>-47925.22</v>
+        <v>-47469.22</v>
       </c>
     </row>
     <row r="74">

--- a/result/Table202511.xlsx
+++ b/result/Table202511.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -525,19 +525,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I2" t="n">
         <v>9.16</v>
       </c>
       <c r="J2" t="n">
-        <v>5.33</v>
+        <v>5.08</v>
       </c>
       <c r="K2" t="n">
-        <v>-41.81</v>
+        <v>-44.54</v>
       </c>
       <c r="L2" t="n">
-        <v>-41812.23</v>
+        <v>-44541.48</v>
       </c>
     </row>
     <row r="3">
@@ -566,7 +566,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,19 +575,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I3" t="n">
         <v>12.59</v>
       </c>
       <c r="J3" t="n">
-        <v>8.69</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>-30.98</v>
+        <v>-32.88</v>
       </c>
       <c r="L3" t="n">
-        <v>-30976.97</v>
+        <v>-32883.24</v>
       </c>
     </row>
     <row r="4">
@@ -716,7 +716,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="I6" t="n">
         <v>5.76</v>
       </c>
       <c r="J6" t="n">
-        <v>3.49</v>
+        <v>3.14</v>
       </c>
       <c r="K6" t="n">
-        <v>-39.41</v>
+        <v>-45.49</v>
       </c>
       <c r="L6" t="n">
-        <v>-39409.72</v>
+        <v>-45486.11</v>
       </c>
     </row>
     <row r="7">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I24" t="n">
         <v>41.42</v>
       </c>
       <c r="J24" t="n">
-        <v>26.28</v>
+        <v>23.3</v>
       </c>
       <c r="K24" t="n">
-        <v>-36.55</v>
+        <v>-43.75</v>
       </c>
       <c r="L24" t="n">
-        <v>-36552.39</v>
+        <v>-43746.98</v>
       </c>
     </row>
     <row r="25">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I35" t="n">
         <v>10.64</v>
       </c>
       <c r="J35" t="n">
-        <v>7.44</v>
+        <v>7.21</v>
       </c>
       <c r="K35" t="n">
-        <v>-30.08</v>
+        <v>-32.24</v>
       </c>
       <c r="L35" t="n">
-        <v>-30075.19</v>
+        <v>-32236.84</v>
       </c>
     </row>
     <row r="36">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3967,19 +3967,19 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I73" t="n">
         <v>21.93</v>
       </c>
       <c r="J73" t="n">
-        <v>11.52</v>
+        <v>10.6</v>
       </c>
       <c r="K73" t="n">
-        <v>-47.47</v>
+        <v>-51.66</v>
       </c>
       <c r="L73" t="n">
-        <v>-47469.22</v>
+        <v>-51664.39</v>
       </c>
     </row>
     <row r="74">

--- a/result/Table202511.xlsx
+++ b/result/Table202511.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -525,19 +525,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I2" t="n">
         <v>9.16</v>
       </c>
       <c r="J2" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="K2" t="n">
-        <v>-44.54</v>
+        <v>-44.65</v>
       </c>
       <c r="L2" t="n">
-        <v>-44541.48</v>
+        <v>-44650.66</v>
       </c>
     </row>
     <row r="3">
@@ -566,7 +566,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,19 +575,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="I3" t="n">
         <v>12.59</v>
       </c>
       <c r="J3" t="n">
-        <v>8.449999999999999</v>
+        <v>6.94</v>
       </c>
       <c r="K3" t="n">
-        <v>-32.88</v>
+        <v>-44.88</v>
       </c>
       <c r="L3" t="n">
-        <v>-32883.24</v>
+        <v>-44876.89</v>
       </c>
     </row>
     <row r="4">
@@ -716,7 +716,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I6" t="n">
         <v>5.76</v>
       </c>
       <c r="J6" t="n">
-        <v>3.14</v>
+        <v>2.85</v>
       </c>
       <c r="K6" t="n">
-        <v>-45.49</v>
+        <v>-50.52</v>
       </c>
       <c r="L6" t="n">
-        <v>-45486.11</v>
+        <v>-50520.83</v>
       </c>
     </row>
     <row r="7">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1601,19 +1601,19 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="I24" t="n">
         <v>41.42</v>
       </c>
       <c r="J24" t="n">
-        <v>23.3</v>
+        <v>23.82</v>
       </c>
       <c r="K24" t="n">
-        <v>-43.75</v>
+        <v>-42.49</v>
       </c>
       <c r="L24" t="n">
-        <v>-43746.98</v>
+        <v>-42491.55</v>
       </c>
     </row>
     <row r="25">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2139,19 +2139,19 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="I35" t="n">
         <v>10.64</v>
       </c>
       <c r="J35" t="n">
-        <v>7.21</v>
+        <v>7.23</v>
       </c>
       <c r="K35" t="n">
-        <v>-32.24</v>
+        <v>-32.05</v>
       </c>
       <c r="L35" t="n">
-        <v>-32236.84</v>
+        <v>-32048.87</v>
       </c>
     </row>
     <row r="36">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3967,19 +3967,19 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="I73" t="n">
         <v>21.93</v>
       </c>
       <c r="J73" t="n">
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="K73" t="n">
-        <v>-51.66</v>
+        <v>-53.03</v>
       </c>
       <c r="L73" t="n">
-        <v>-51664.39</v>
+        <v>-53032.38</v>
       </c>
     </row>
     <row r="74">
